--- a/docs/Sundial_Solar_Fields_by_Section.xlsx
+++ b/docs/Sundial_Solar_Fields_by_Section.xlsx
@@ -10181,10 +10181,10 @@
         <v>15</v>
       </c>
       <c r="I163" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J163" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -10213,10 +10213,10 @@
         <v>15</v>
       </c>
       <c r="I164" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J164" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -10245,10 +10245,10 @@
         <v>15</v>
       </c>
       <c r="I165" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J165" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -10277,10 +10277,10 @@
         <v>15</v>
       </c>
       <c r="I166" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J166" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -10309,10 +10309,10 @@
         <v>15</v>
       </c>
       <c r="I167" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J167" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -11013,10 +11013,10 @@
         <v>15</v>
       </c>
       <c r="I189" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J189" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -11077,10 +11077,10 @@
         <v>15</v>
       </c>
       <c r="I191" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J191" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -16584,7 +16584,7 @@
         <v>21</v>
       </c>
       <c r="J363" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.25">
@@ -16616,7 +16616,7 @@
         <v>21</v>
       </c>
       <c r="J364" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.25">
@@ -16648,7 +16648,7 @@
         <v>21</v>
       </c>
       <c r="J365" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.25">
@@ -16738,7 +16738,7 @@
         <v>21</v>
       </c>
       <c r="J368" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.25">
@@ -16770,7 +16770,7 @@
         <v>21</v>
       </c>
       <c r="J369" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.25">
@@ -16802,7 +16802,7 @@
         <v>21</v>
       </c>
       <c r="J370" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.25">
@@ -16892,7 +16892,7 @@
         <v>21</v>
       </c>
       <c r="J373" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.25">
@@ -16924,7 +16924,7 @@
         <v>21</v>
       </c>
       <c r="J374" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.25">
@@ -16956,7 +16956,7 @@
         <v>21</v>
       </c>
       <c r="J375" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.25">
@@ -17046,7 +17046,7 @@
         <v>21</v>
       </c>
       <c r="J378" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.25">
@@ -17078,7 +17078,7 @@
         <v>21</v>
       </c>
       <c r="J379" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.25">
@@ -17110,7 +17110,7 @@
         <v>21</v>
       </c>
       <c r="J380" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.25">
@@ -17200,7 +17200,7 @@
         <v>21</v>
       </c>
       <c r="J383" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.25">
@@ -17232,7 +17232,7 @@
         <v>21</v>
       </c>
       <c r="J384" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.25">
@@ -17264,7 +17264,7 @@
         <v>21</v>
       </c>
       <c r="J385" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.25">
